--- a/Studymaterials/生活記録表生徒用_横型.xlsx
+++ b/Studymaterials/生活記録表生徒用_横型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakag\Desktop\GitHub\Myownproject\Studymaterials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B26A05-364F-446F-9EBA-E99E4613C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0ED980-EF09-48D1-A4B5-2DC02CA3EF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="横型日曜始まり" sheetId="1" r:id="rId1"/>
@@ -282,21 +282,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -363,6 +348,17 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -371,38 +367,38 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -719,569 +715,569 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="J5" s="5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="J5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="J9" s="5" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="J9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="J13" s="5" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="J13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="J17" s="5" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="J17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
     </row>
     <row r="21" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="J21" s="5" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="J21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="J25" s="5" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="J25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1305,7 +1301,7 @@
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1325,569 +1321,569 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="J5" s="5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="J5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="J9" s="5" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="J9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="J13" s="5" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="J13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="J17" s="5" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="J17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
     </row>
     <row r="21" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="J21" s="5" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="J21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="J25" s="5" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="J25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Studymaterials/生活記録表生徒用_横型.xlsx
+++ b/Studymaterials/生活記録表生徒用_横型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakag\Desktop\GitHub\Myownproject\Studymaterials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0ED980-EF09-48D1-A4B5-2DC02CA3EF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435949CC-CCF5-45B6-BB73-596AFC7619F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="横型日曜始まり" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
   <si>
-    <t>生活記録表（横型）</t>
-  </si>
-  <si>
     <t>項目</t>
   </si>
   <si>
@@ -164,6 +161,10 @@
   </si>
   <si>
     <t>睡眠</t>
+  </si>
+  <si>
+    <t>生活記録表</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -380,16 +381,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -399,6 +390,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -715,70 +716,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="A1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
       <c r="I1" s="5"/>
       <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -787,15 +788,15 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -804,17 +805,17 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="J5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -823,15 +824,15 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -840,15 +841,15 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -857,15 +858,15 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -874,17 +875,17 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="J9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -893,15 +894,15 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -910,15 +911,15 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -927,15 +928,15 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -944,17 +945,17 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="J13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="J13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -963,15 +964,15 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -980,15 +981,15 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -997,15 +998,15 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1014,17 +1015,17 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="J17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
+      <c r="J17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1033,15 +1034,15 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1050,15 +1051,15 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1067,15 +1068,15 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1084,17 +1085,17 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="J21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
+      <c r="J21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1103,15 +1104,15 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1120,15 +1121,15 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1137,15 +1138,15 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1154,17 +1155,17 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="J25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="J25" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1173,15 +1174,15 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1190,15 +1191,15 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1207,11 +1208,11 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
@@ -1222,15 +1223,15 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1239,15 +1240,15 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1256,15 +1257,15 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1273,20 +1274,14 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="J17:J20"/>
     <mergeCell ref="J25:J32"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K17:N20"/>
@@ -1297,6 +1292,12 @@
     <mergeCell ref="K5:N8"/>
     <mergeCell ref="J13:J16"/>
     <mergeCell ref="K13:N16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="J17:J20"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1321,70 +1322,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="A1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
       <c r="I1" s="5"/>
       <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1393,15 +1394,15 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1410,17 +1411,17 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="J5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1429,15 +1430,15 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1446,15 +1447,15 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1463,15 +1464,15 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1480,17 +1481,17 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="J9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1499,15 +1500,15 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1516,15 +1517,15 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1533,15 +1534,15 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1550,17 +1551,17 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="J13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="J13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1569,15 +1570,15 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1586,15 +1587,15 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1603,15 +1604,15 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1620,17 +1621,17 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="J17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
+      <c r="J17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1639,15 +1640,15 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1656,15 +1657,15 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1673,15 +1674,15 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1690,17 +1691,17 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="J21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
+      <c r="J21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1709,15 +1710,15 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1726,15 +1727,15 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1743,15 +1744,15 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1760,17 +1761,17 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="J25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="J25" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1779,15 +1780,15 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1796,15 +1797,15 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1813,11 +1814,11 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
@@ -1828,15 +1829,15 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1845,15 +1846,15 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1862,15 +1863,15 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1879,20 +1880,14 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="J17:J20"/>
     <mergeCell ref="J25:J32"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K17:N20"/>
@@ -1903,6 +1898,12 @@
     <mergeCell ref="K5:N8"/>
     <mergeCell ref="J13:J16"/>
     <mergeCell ref="K13:N16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="J17:J20"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
